--- a/Mês 5/3. Problema de Localização p-Medianas/Data/Instancia_CDs_pMedianas.xlsx
+++ b/Mês 5/3. Problema de Localização p-Medianas/Data/Instancia_CDs_pMedianas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ufcbr-my.sharepoint.com/personal/levi_abreu_ufc_br/Documents/UFC/ENGINE/GoPro/Mês 5/3. Problema de Localização p-Medianas/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_EBBD426C6CD9D373D097C45A4D81775B83D1FB2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE05968-CD32-4C3A-B8FB-89093ED02BC0}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_EBBD426C6CD9D373D097C45A4D81775B83D1FB2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0736915-430C-4217-BBBB-D3B9FA134729}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="924" windowWidth="20976" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="924" windowWidth="20976" windowHeight="10920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados_Candidatos_Clientes" sheetId="1" r:id="rId1"/>
@@ -645,6 +645,72 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>981519</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>24524</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A4CFAA-B3A3-35E5-C76B-F967A91FAA7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5363019" y="198120"/>
+          <a:ext cx="6859461" cy="4627004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -19794,5 +19860,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>